--- a/assignment3/data/trainingdataset_ontario_budgets_v7_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v7_llm_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CF4A92-9127-E444-867B-F4658E11229D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707B6877-D4F6-2A4C-B50D-5F0777F43065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15820" yWindow="520" windowWidth="22560" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="8560" yWindow="500" windowWidth="29000" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="927">
   <si>
     <t>document</t>
   </si>
@@ -3998,12 +3998,349 @@
   <si>
     <t>PART 2 NEW</t>
   </si>
+  <si>
+    <t>york_2017</t>
+  </si>
+  <si>
+    <t>york_2017_1</t>
+  </si>
+  <si>
+    <t>York’s operating budget is comprised mostly of two revenue streams – 33% in government grants and 60% in tuition fee revenue, much of which is regulated or directed by government. This means limited flexibility for universities to increase revenue.</t>
+  </si>
+  <si>
+    <t>york_2017_2</t>
+  </si>
+  <si>
+    <t>In the recent past, the government has limited funding increases to enrolment growth. The 2017 Provincial Budget announced that there would be no funds allocated for enrolment growth above the 2016-17 levels. According to government population projections, the provincial demographics of university age students are expected to decline for two more years. However, the government’s OSAP reforms are having a
+7
+positive impact on enrolments and accessibility at Ontario’s universities. The number of high school students applying to Ontario’s universities is up 1.6% over last year despite an overall decline in secondary school graduates. This demonstrates that postsecondary education is recognized as key to a brighter economic future for graduates, and for the province.</t>
+  </si>
+  <si>
+    <t>york_2017_3</t>
+  </si>
+  <si>
+    <t>As indicated previously, the Ministry is implementing a new funding model in 2017-18. In this formula, more grant funding is linked to outcomes unlike previously when grant funding was linked strictly to enrolment. In the new formula, the Ministry has created three funding bins – a funding bin linked to enrolment, one linked to quality and differentiation measured using agreed upon outcomes based metrics and a special purpose or targeted funding bin which supports targeted funding for initiatives such as French language, disability supports, etc. The Ministry has committed to maintaining the 2016-17 funding level for all universities through the second round of SMAs that are currently being negotiated and will be in place for three years (2017-18 to 2019-20).</t>
+  </si>
+  <si>
+    <t>york_2017_4</t>
+  </si>
+  <si>
+    <t>The government’s tuition fee framework initially announced in March 2013-14, and set to expire in 2016-17 has now been extended for another two years. This framework limits the tuition fee increases to an institutional average of 3%. The proposed Budget Plan has assumed the same tuition fee framework for the next three years.</t>
+  </si>
+  <si>
+    <t>york_2017_5</t>
+  </si>
+  <si>
+    <t>A key planning assumption which drives revenue and cost changes is the enrolment plan. The current overall multi-year enrolment plan is provided in Table 2. The plan outlines the overall projected enrolment by domestic and international students for both undergraduate and graduate enrolments.</t>
+  </si>
+  <si>
+    <t>york_2017_6</t>
+  </si>
+  <si>
+    <t>Overall, the actual 2016-17 enrolments were above budget targets with most of the growth coming from undergraduate and graduate international students.</t>
+  </si>
+  <si>
+    <t>york_2017_7</t>
+  </si>
+  <si>
+    <t>As a result of enrolment decline challenges in the domestic undergraduate category, York will continue to experience fewer enrolments in 2017-18 compared to previous years. This is attributed to more students in the graduating cohort compared to those in the entering cohorts in the last few years. It is expected that as the smaller cohorts flow through and begin to graduate, enrolment will reach 45,000 full time equivalent undergraduate (domestic and international) students by 2018-19, surpassing the 2012-13 levels of 44,300.</t>
+  </si>
+  <si>
+    <t>york_2017_8</t>
+  </si>
+  <si>
+    <t>With respect to graduate students, the University’s current plan for domestic graduate enrolment is to achieve the first round of SMA enrolment levels, which are similar to the enrolment levels reached in 2008-09 for masters and slightly lower for doctoral. This
+8
+plan will be informed by the current discussions with the Ministry under the second
+round of SMA negotiations.</t>
+  </si>
+  <si>
+    <t>york_2017_9</t>
+  </si>
+  <si>
+    <t>This enrolment plan is to grow domestic enrolments back to the levels that are currently
+funded by the Ministry and is in line with our SMA1 commitments. The enrolment plan
+will be revisited once the SMA2 negotiations with MAESD have been completed. The
+negotiations are expected to be finalized by the end of June 2017.</t>
+  </si>
+  <si>
+    <t>laurier_2025</t>
+  </si>
+  <si>
+    <t>laurier_2025_1</t>
+  </si>
+  <si>
+    <t>The assumptions and estimates included in the 2025/26 Operating, Ancillary and Capital budgets are
+based on the information available to management at the time of preparation. Post-secondary
+institutions in Canada are facing sector-wide challenges, with continued revenue constraints and
+significant inflationary pressures contributing to growing financial risks. Universities across Ontario are
+facing increased scrutiny on fiscal performance through the Ministry of Colleges, Universities, Research
+Excellence and Security (MCURES) Financial Accountability Framework.</t>
+  </si>
+  <si>
+    <t>laurier_2025_2</t>
+  </si>
+  <si>
+    <t>Successfully navigating this difficult environment will require highly disciplined and effective financial
+management as the university considers both the short-term horizon as articulated in the fiscal year
+budget and long-term sustainability as depicted in the multi-year budget projections.</t>
+  </si>
+  <si>
+    <t>laurier_2025_3</t>
+  </si>
+  <si>
+    <t>On April 22, 2025 MCURES announced a $750 million investment to support 20,500 STEM learners
+annually at universities and colleges. Due to Laurier’s significant enrolment growth in serving Ontario
+students, particularly in STEM programs, Laurier’s share of that funding is $16.1 million annually,
+representing funding for over 2,000 existing unfunded STEM learners at the current system funding rates.
+Laurier’s share of the funding is committed for three years, with funding for 2028/29 and 2029/30 to be
+confirmed by MCURES through future multi-year planning exercises informed by the upcoming funding
+model review.</t>
+  </si>
+  <si>
+    <t>Notwithstanding this recent infusion of government grant funding, Laurier remain in a structural deficit
+position, with a modest deficit slated to increase rapidly over the next five years even if tuition is
+permitted to increase in 2027/28 and beyond. Significant constraints on revenue continue in the short
+term, including an ongoing general freeze in domestic tuition rates and a federal cap on international
+study permits for undergraduate students. The limitations on revenue mean that Laurier will not be able
+to keep pace with rising operating costs, make the appropriate level of investments in facilities renewal
+and information technology systems, or invest in strategic initiatives and programs required to succeed
+in a highly competitive sector.</t>
+  </si>
+  <si>
+    <t>laurier_2025_4</t>
+  </si>
+  <si>
+    <t>laurier_2025_5</t>
+  </si>
+  <si>
+    <t>Alongside a challenging revenue outlook, increased scrutiny of universities’ financial performance
+continues through the MCURES University Financial Accountability Framework. The Framework consists
+of the five financial health indicators previously reported by Ontario Universities and incorporates debt
+ratios and the institution’s credit rating into an overall risk assessment. While Laurier’s 2023/24 financial
+performance resulted in a “low” risk assessment, a significant contributing factor to this assessment was
+the occurrence of one-time financial impacts such as real estate transactions (reinvested in capital) and
+the 23/24 one-time-only STEM funding. Without these transactions, Laurier’s performance would have
+yielded a less favourable risk assessment rating. With the current structural deficit position Laurier must
+continue efforts to prioritize key investments with consideration for growth, revenue generation, cost
+containment, and spending to increase priority services and programs while demonstrating the ability to
+safeguard its fiscal health through Framework risk assessment results.</t>
+  </si>
+  <si>
+    <t>laurier_2025_6</t>
+  </si>
+  <si>
+    <t>Throughout our history, the strength of the Wilfrid Laurier University community has allowed us to
+capitalize on opportunities and overcome challenges to become a comprehensive, multi-campus
+institution focused on excellence in academics, a sector-leading student experience, and a growing
+research enterprise. Since 2019, Laurier has pursued these efforts in addition to implementing significant
+budget savings targets; with the 2025/26 proposed budget, the magnitude of efficiencies achieved will
+be in excess of $43 million, a 12% reduction resulting in 2025/26 budgeted expenses of $371 million.</t>
+  </si>
+  <si>
+    <t>laurier_2025_7</t>
+  </si>
+  <si>
+    <t>The Operating Budget comprises the major annual revenues and expenditures of the university’s financial
+operations. Revenues from student tuition fees and government operating grants account for 85% of the
+total operating revenues. Faculty and staff salaries and benefits account for 75% of the total operating
+expenditures. Table 1 below is a summary of the 2025/26 Operating Budget.</t>
+  </si>
+  <si>
+    <t>laurier_2025_8</t>
+  </si>
+  <si>
+    <t>The 2025/26 Budget shows forecasted total revenues of $369.1 million, an increase of $32.6 million, or
+9.7%, over last year’s Budget. Tuition revenue has increased by $5.6 million, primarily due to an
+anticipated 1.6% increase in enrolment and limited, allowable tuition increases. An overall $18.9 million
+increase in grant funding over the prior year is the result of the recently announced support for the
+continued delivery and enhancement of STEM programming for the sector, with Laurier receiving $16.1
+million. Other grant increases relate to the increase in one-time funding from the Postsecondary
+Education Sustainability Fund (PSESF) and continued domestic growth at the Milton campus, which is fully
+funded. An updated Student Affairs Administrative Agreement (SAAA), now called the Comprehensive
+Student Services Administrative Agreement (CSSAA), resulting in additional student contributions driving
+the remaining revenue increase.</t>
+  </si>
+  <si>
+    <t>laurier_2025_9</t>
+  </si>
+  <si>
+    <t>Total expenditures are forecasted at $371.4 million, an increase of $27.6 million, or 8.0%, over last year.
+Salaries and benefits increased by $22.1 million over the previous year, largely due to current collective
+agreements in place, (~$15 million), benefit increases and transitioning to UPP on January 1, 2026 (~$2.5
+million). Non-salary expenses increased by $5.4 million. Section 3.2.6 provides further detail.</t>
+  </si>
+  <si>
+    <t>laurier_2025_10</t>
+  </si>
+  <si>
+    <t>The 2025/26 Budget is being presented as a balanced budget through the continuation of limited austerity
+measures, appropriation of the Milton operating deficit, and the anticipated additional BEd funding that
+remains unconfirmed at the time of writing. Further, an institutional 1.0% budget reduction across vice-
+president portfolios along with limited investments in 2025/26 also contributed to the balanced budget
+being put forward for approval.</t>
+  </si>
+  <si>
+    <t>laurier_2025_11</t>
+  </si>
+  <si>
+    <t>The Ancillary Services Budget as summarized in Table 2 below includes the self-sustaining units of
+Business Development, Conference Services, Food Services, Hawk Shops, HUB Operations, Off Campus
+Housing (Ezra Bricker Apartments &amp; Houses), OneCard Operations, Parking &amp; Transportation Resources,
+Printing Services and Residence Operations (Waterloo &amp; Brantford campuses).</t>
+  </si>
+  <si>
+    <t>laurier_2025_12</t>
+  </si>
+  <si>
+    <t>The revenue of the ancillary enterprises increased by $2.9 million from an approved budget of $57.1
+million in 2024/25 to $60.1 million in 2025/26.</t>
+  </si>
+  <si>
+    <t>Wilfrid Laurier University</t>
+  </si>
+  <si>
+    <t>laurier_2024</t>
+  </si>
+  <si>
+    <t>laurier_2024_1</t>
+  </si>
+  <si>
+    <t>The assumptions and estimates included in the 2024/2025 Operating, Ancillary and Capital budgets are based on the information available to management at the time of preparation. Post-secondary institutions in Canada are facing sector-wide challenges, with continued revenue constraints and significant inflationary pressures contributing to growing financial risks. Universities across Ontario are facing increased scrutiny on fiscal performance through a recently announced MCU Financial Accountability Framework and a series of value-for-money audits by the Auditor General.</t>
+  </si>
+  <si>
+    <t>laurier_2024_2</t>
+  </si>
+  <si>
+    <t>Successfully navigating this difficult environment will require highly disciplined and effective financial
+management as the university considers both the short-term horizon as articulated in the fiscal year
+budget and long-term sustainability as depicted in the multi-year budget projections</t>
+  </si>
+  <si>
+    <t>laurier_2024_3</t>
+  </si>
+  <si>
+    <t>Laurier is now in a structural deficit position, as the university faces significant constraints on revenue including an ongoing general freeze in domestic tuition rates, modest temporary increases to government grant, and a federal cap on international study permits for undergraduate students. The limitations on revenue mean that Laurier will not be able to keep pace with rising operating costs, make the appropriate level of investments in facilities renewal and information technology systems, or invest in strategic initiatives and programs to succeed in a highly competitive sector.</t>
+  </si>
+  <si>
+    <t>Alongside a challenging revenue outlook, increased scrutiny of universities’ financial performance
+continues through the MCURES University Financial Accountability Framework. The Framework consists
+of the five financial health indicators previously reported by Ontario Universities and incorporates debt ratios and the institution's credit rating into an overall risk assessment. Laurier's 2022/2023 financial performance resulted in a "low" risk assessment, however, a significant contributing factor to this assessment was the occurance of one-time real estate transactions - without these transactions, Laurier's performance would have yielded a less favourable risk assessment rating. With the current structural deficit position Laurier must continue efforts to prioritize key investments with consideration for growth, revenue generation, cost containment, and spending to increase priority services and programs while demonstrating the ability to safeguard its fiscal health through Framework risk assessment results.</t>
+  </si>
+  <si>
+    <t>laurier_2024_4</t>
+  </si>
+  <si>
+    <t>laurier_2024_5</t>
+  </si>
+  <si>
+    <t>In February 2024, Laurier received $11.6 million of funding for the 2023/24 fiscal year as part of the province's funding approach to stabilize colleges and universities while maintaining a tuition freeze for Ontario students. This funding was provided specifically for STEM program costs for enrolments above currently funded levels. This one-time funding enables Laurier to offset $11.6 million in budgeted expenditures incurred during the 2023/24 and contribute to a stabilization fund to mitigate future deficits. While this provides some limited, short-term deficit mitigation, without sustained and predictable funding Laurier will continue to be challenged with a growing structural deficit.</t>
+  </si>
+  <si>
+    <t>laurier_2024_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throughout our history, the strength of the Wilfrid Laurier University community has allowed us to
+capitalize on opportunities and overcome challenges to become a comprehensive, multi-campus
+institution focused on excellence in academics, a sector-leading student experience, and a growing research enterprise. Since 2019, Laurier has pursued these efforts in addition to implementing significant budget savings targets; with the 2024/25 proposed budget, the magnitude of efficiencies achieved will be in excess of $39 million, a 12% reduction in 2024/25 budgeted expenses of $344 million. </t>
+  </si>
+  <si>
+    <t>laurier_2024_7</t>
+  </si>
+  <si>
+    <t>The Operating Budget comprises the major annual revenues and expenditures of the university’s financial
+operations. Revenues from student tuition fees and government operating grants account for 85% of the
+total operating revenues. Faculty and staff salaries and benefits account for 75% of the total operating expenditures. Table 1 below is a summary of the 2024/25 Operating Budget.</t>
+  </si>
+  <si>
+    <t>laurier_2024_8</t>
+  </si>
+  <si>
+    <t>The 2024/25 Budget shows forecasted total revenues of $336.5 million, an increase of $9.1 million, or 2.8% over last year's Budget. Tuition revenue has remained substantially unchanged with a slight increase of $0.2 million. An overall $3.9 million increase in grant funding over the prior year is mainly due to the increase in one-time funding from the Postsecondary Education Sustainability Fund. Government operating grant base funding remains steady, with a slight increase reflecting the inaugural student cohort at the new Milton campus. An updated Student Affaris Advisory Committee (SAAC) agreement, resulting in additional student contributions of $3.6 million in 2023/24, drove the remaining revenue increase.</t>
+  </si>
+  <si>
+    <t>laurier_2024_9</t>
+  </si>
+  <si>
+    <t>Total expenditures are forecasted at $343.9 million, an increase of $9.7 million, or 2.9%, over last year.
+Salaries and benefits increased by $14.9 million over the previous year, largely due to current collective
+agreements in place, and non-salary expenses decreased by $5.2 million.</t>
+  </si>
+  <si>
+    <t>laurier_2024_10</t>
+  </si>
+  <si>
+    <t>The 2024/25 Budget is being presented as a balanced budget primarily through limited austerity measures, appropriation of the Milton operating deficit, and drawdown of the Operating Budget Stabilization Reserve. Further, an institutional 4.5% budget reduction across vice-president portfolios along with limited investments in 2024/25 also contributed to the balanced budget being put forward for approval.</t>
+  </si>
+  <si>
+    <t>laurier_2023</t>
+  </si>
+  <si>
+    <t>laurier_2023_1</t>
+  </si>
+  <si>
+    <t>The 2023/24 budget anticipates a full return to on-campus operations following multiple years of pandemic-driven budget assumptions. In recent years, the organization has been successful in mitigating the cumulate fiscal impacts of tuition cuts, grant and tuition freezes, pandemic-related public health restrictions, and challenges affecting sector efforts in internationalization. The provincial government has recently announced a blue-ribbon panel, composed of business and academic leaders, that will provide advice and recommendations related to sector financial stability beyond 2023/24. For 2023/24, funding constraints are continuing, with a continued tuition freeze for most Ontario students and fixed operating grant funding.</t>
+  </si>
+  <si>
+    <t>laurier_2023_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With financial challenges escalating, the sector is also subject to increased scrutiny reuslting from recent auditor general value-for-money audits. While annual operating budget plans are critical to financial sustainability, the asssessment of comprehensive fiscal health inclusive of capital planning, reserve conditions, and debt capacity, will be needed to support Laurier's significant upcoming growth initiatives. Laurier is poised to embark upon a number of exciting initiatives which will contribute to its strategic mandate and success in a highly competitive sector. The prioritization and focus on key investments with consideration for revenue generation, cost containment and spending to increase priority services and programs, will be critical in optimizing limited resources and safeguarding Laurier's financial health - key principles in the development of the 2023/24 Budget. </t>
+  </si>
+  <si>
+    <t>laurier_2023_3</t>
+  </si>
+  <si>
+    <t>This draft report includes the Operating and Ancillary Funds which are Laurier's largest funds and components of the overall Consolidated Financial Statement Funds. The Capital Budget will be presented to the Board for approval at the June meeting. At this time, the Milton operating plan and capital project budget are not included. Program and campus development are currently underway with a projected Milton campus opening in Fall 2024. Based on a risk analysis of pursuing campus expansion in the current environment, programming will commence in pre-existing leased space with construction of Milton One timed in accordance with enrolment trajectory and debt-servicing capacity. A revised business plan is in development for presentation in the May/June governance cycle.</t>
+  </si>
+  <si>
+    <t>laurier_2023_4</t>
+  </si>
+  <si>
+    <t>The assumptions and estimates included in the 2023/24 Operating and Ancillary budgets are based on the information available to management at the time of preparation. Post-secondary institutions in Canada are facing sector-wide challenges; the cumulative impact of tuition cuts, grant and tuition freezes, COVID-19 pandemic impacts and significant inflationary pressures have contributed to growing financial risks. Universities across Ontario are facing increased scrutiny on fiscal performance and a greater focus on financial health indicators is expected as part of the province’s overall performance management framework. This will require demonstration of effective financial planning which considers the short-term needs articulated in a fiscal year budget, as well as longer term strategies that tie into strategic priorities and capital planning. Throughout our history, the strength of the Wilfrid Laurier University community has allowed us to capitalize on opportunities and prevail over challenges to become a comprehensive, multi-campus institution focused on excellence in academics, a student experience second to none, and growing research enterprise. The 2023/24 budget builds upon those strengths as the university embarks on a number of efforts which will contribute to its continued success.</t>
+  </si>
+  <si>
+    <t>laurier_2023_5</t>
+  </si>
+  <si>
+    <t>Prioritization and a focus on key investments, with consideration for growth strategies, revenue generation, cost containment and spending to increase priority services and programs will be critical to optimize limited resources and safeguard Laurier’s fiscal health.</t>
+  </si>
+  <si>
+    <t>laurier_2023_6</t>
+  </si>
+  <si>
+    <t>Financial sustainability is a critical enabler that will equip Laurier with the financial strength and capacity to achieve its strategic objectives. Financial sustainability refers to the balance between the revenues available to institutions to support their academic activities and the expenses they incur in delivering their mission.</t>
+  </si>
+  <si>
+    <t>laurier_2023_7</t>
+  </si>
+  <si>
+    <t>Laurier continues work to strengthen financial sustainability to support the strategic objectives of the organization. In 2023/24, Laurier will continue 2022/23 efforts to deliver enhanced, consolidated quarterly financial reports, develop preliminary debt and reserve strategies, and improve capital budgeting practices. The recent reports by the Auditor General have also provided additional considerations for Laurier in the pursuit of financial sustainability and effective financial management.</t>
+  </si>
+  <si>
+    <t>laurier_2023_8</t>
+  </si>
+  <si>
+    <t>The 2023/24 Budget shows forecasted total revenues of $327.4 million, a decrease of $5.1 million, or 1.5%, over last year’s Budget. Tuition revenue has decreased significantly by $13.7 million or 6.9%, reflecting the flow-through of the tuition shortfall experienced in 2022/23. Government operating grants remain steady with a slight increase of $0.2 million.</t>
+  </si>
+  <si>
+    <t>laurier_2023_9</t>
+  </si>
+  <si>
+    <t>Total expenditures are forecasted at $334.1 million, an increase of $3.7 million, or 1.1%, over last year. Salaries and benefits remained relatively constant over the previous year, with multiple factors contributing both favourably and unfavourably and non-salary expenses increasing by $3.8 million.</t>
+  </si>
+  <si>
+    <t>laurier_2023_10</t>
+  </si>
+  <si>
+    <t>The 2023/24 Budget being presented is a deficit budget of $1.9 million. Laurier will be pursuing a multi-year approach to addressing financial sustainability, with in-year strategies to minimize the draw on reserves coupled with a return to realizing a surplus budget strategy.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4088,6 +4425,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -4139,7 +4483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4183,6 +4527,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4520,7 +4866,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q402"/>
+  <dimension ref="A1:Q451"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -14589,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="E285" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F285" s="4">
         <v>46</v>
@@ -14625,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="E286" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F286" s="4">
         <v>46</v>
@@ -14661,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="E287" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F287" s="4">
         <v>46</v>
@@ -14697,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="E288" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F288" s="4">
         <v>46</v>
@@ -14733,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="E289" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F289" s="4">
         <v>46</v>
@@ -14769,7 +15115,7 @@
         <v>0</v>
       </c>
       <c r="E290" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F290" s="4">
         <v>46</v>
@@ -14805,7 +15151,7 @@
         <v>0</v>
       </c>
       <c r="E291" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F291" s="4">
         <v>46</v>
@@ -14841,7 +15187,7 @@
         <v>0</v>
       </c>
       <c r="E292" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F292" s="4">
         <v>46</v>
@@ -14877,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="E293" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F293" s="4">
         <v>46</v>
@@ -14913,7 +15259,7 @@
         <v>0</v>
       </c>
       <c r="E294" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F294" s="4">
         <v>46</v>
@@ -14949,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="E295" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F295" s="4">
         <v>46</v>
@@ -14985,7 +15331,7 @@
         <v>0</v>
       </c>
       <c r="E296" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F296" s="4">
         <v>46</v>
@@ -15021,7 +15367,7 @@
         <v>0</v>
       </c>
       <c r="E297" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F297" s="4">
         <v>46</v>
@@ -15057,7 +15403,7 @@
         <v>1</v>
       </c>
       <c r="E298" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F298" s="4">
         <v>46</v>
@@ -15093,7 +15439,7 @@
         <v>0</v>
       </c>
       <c r="E299" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F299" s="4">
         <v>46</v>
@@ -15129,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="E300" s="4">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F300" s="4">
         <v>46</v>
@@ -15165,7 +15511,7 @@
         <v>0</v>
       </c>
       <c r="E301" s="4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F301" s="4">
         <v>46</v>
@@ -15201,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="E302" s="4">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F302" s="4">
         <v>46</v>
@@ -15237,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="E303" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F303" s="4">
         <v>46</v>
@@ -15273,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="E304" s="4">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F304" s="4">
         <v>46</v>
@@ -15309,7 +15655,7 @@
         <v>0</v>
       </c>
       <c r="E305" s="4">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F305" s="4">
         <v>46</v>
@@ -15345,7 +15691,7 @@
         <v>1</v>
       </c>
       <c r="E306" s="4">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F306" s="4">
         <v>46</v>
@@ -15381,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="E307" s="4">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F307" s="4">
         <v>46</v>
@@ -15417,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="E308" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F308" s="4">
         <v>46</v>
@@ -15453,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="E309" s="4">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F309" s="4">
         <v>46</v>
@@ -15489,7 +15835,7 @@
         <v>0</v>
       </c>
       <c r="E310" s="4">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F310" s="4">
         <v>46</v>
@@ -15525,7 +15871,7 @@
         <v>0</v>
       </c>
       <c r="E311" s="4">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F311" s="4">
         <v>46</v>
@@ -15561,7 +15907,7 @@
         <v>0</v>
       </c>
       <c r="E312" s="4">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F312" s="4">
         <v>46</v>
@@ -15597,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="E313" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F313" s="4">
         <v>46</v>
@@ -15633,7 +15979,7 @@
         <v>0</v>
       </c>
       <c r="E314" s="4">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F314" s="4">
         <v>46</v>
@@ -15669,7 +16015,7 @@
         <v>0</v>
       </c>
       <c r="E315" s="4">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F315" s="4">
         <v>46</v>
@@ -15705,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="E316" s="4">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F316" s="4">
         <v>46</v>
@@ -15741,7 +16087,7 @@
         <v>0</v>
       </c>
       <c r="E317" s="4">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F317" s="4">
         <v>46</v>
@@ -15777,7 +16123,7 @@
         <v>0</v>
       </c>
       <c r="E318" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F318" s="4">
         <v>46</v>
@@ -15813,7 +16159,7 @@
         <v>0</v>
       </c>
       <c r="E319" s="4">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F319" s="4">
         <v>46</v>
@@ -15849,7 +16195,7 @@
         <v>0</v>
       </c>
       <c r="E320" s="4">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F320" s="4">
         <v>46</v>
@@ -15885,7 +16231,7 @@
         <v>0</v>
       </c>
       <c r="E321" s="4">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="F321" s="4">
         <v>46</v>
@@ -15921,7 +16267,7 @@
         <v>1</v>
       </c>
       <c r="E322" s="4">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F322" s="4">
         <v>46</v>
@@ -15957,7 +16303,7 @@
         <v>0</v>
       </c>
       <c r="E323" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F323" s="4">
         <v>46</v>
@@ -15993,7 +16339,7 @@
         <v>0</v>
       </c>
       <c r="E324" s="4">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F324" s="4">
         <v>46</v>
@@ -16029,7 +16375,7 @@
         <v>0</v>
       </c>
       <c r="E325" s="4">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F325" s="4">
         <v>46</v>
@@ -16065,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="E326" s="4">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F326" s="4">
         <v>46</v>
@@ -16101,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="E327" s="4">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F327" s="4">
         <v>46</v>
@@ -16137,7 +16483,7 @@
         <v>0</v>
       </c>
       <c r="E328" s="4">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F328" s="4">
         <v>46</v>
@@ -16173,7 +16519,7 @@
         <v>0</v>
       </c>
       <c r="E329" s="4">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F329" s="4">
         <v>46</v>
@@ -16244,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="E331" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F331" s="4">
         <v>6</v>
@@ -16279,7 +16625,7 @@
         <v>0</v>
       </c>
       <c r="E332" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F332" s="4">
         <v>6</v>
@@ -16314,7 +16660,7 @@
         <v>0</v>
       </c>
       <c r="E333" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F333" s="4">
         <v>6</v>
@@ -16349,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="E334" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F334" s="4">
         <v>6</v>
@@ -16384,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="E335" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F335" s="4">
         <v>6</v>
@@ -16454,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="E337" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F337" s="4">
         <v>17</v>
@@ -16489,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="E338" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F338" s="4">
         <v>17</v>
@@ -16524,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="E339" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F339" s="4">
         <v>17</v>
@@ -16559,7 +16905,7 @@
         <v>1</v>
       </c>
       <c r="E340" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F340" s="4">
         <v>17</v>
@@ -16594,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="E341" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F341" s="4">
         <v>17</v>
@@ -16629,7 +16975,7 @@
         <v>1</v>
       </c>
       <c r="E342" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F342" s="4">
         <v>17</v>
@@ -16664,7 +17010,7 @@
         <v>1</v>
       </c>
       <c r="E343" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F343" s="4">
         <v>17</v>
@@ -16699,7 +17045,7 @@
         <v>0</v>
       </c>
       <c r="E344" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F344" s="4">
         <v>17</v>
@@ -16734,7 +17080,7 @@
         <v>0</v>
       </c>
       <c r="E345" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F345" s="4">
         <v>17</v>
@@ -16769,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="E346" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F346" s="4">
         <v>17</v>
@@ -16804,7 +17150,7 @@
         <v>1</v>
       </c>
       <c r="E347" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F347" s="4">
         <v>17</v>
@@ -16839,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="E348" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F348" s="4">
         <v>17</v>
@@ -16874,7 +17220,7 @@
         <v>0</v>
       </c>
       <c r="E349" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F349" s="4">
         <v>17</v>
@@ -16909,7 +17255,7 @@
         <v>0</v>
       </c>
       <c r="E350" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F350" s="4">
         <v>17</v>
@@ -16944,7 +17290,7 @@
         <v>0</v>
       </c>
       <c r="E351" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F351" s="4">
         <v>17</v>
@@ -16979,7 +17325,7 @@
         <v>0</v>
       </c>
       <c r="E352" s="4">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F352" s="4">
         <v>17</v>
@@ -17049,7 +17395,7 @@
         <v>0</v>
       </c>
       <c r="E354" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F354" s="4">
         <v>7</v>
@@ -17084,7 +17430,7 @@
         <v>0</v>
       </c>
       <c r="E355" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F355" s="4">
         <v>7</v>
@@ -17119,7 +17465,7 @@
         <v>0</v>
       </c>
       <c r="E356" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F356" s="4">
         <v>7</v>
@@ -17154,7 +17500,7 @@
         <v>0</v>
       </c>
       <c r="E357" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F357" s="4">
         <v>7</v>
@@ -17189,7 +17535,7 @@
         <v>0</v>
       </c>
       <c r="E358" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F358" s="4">
         <v>7</v>
@@ -17224,7 +17570,7 @@
         <v>0</v>
       </c>
       <c r="E359" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F359" s="4">
         <v>7</v>
@@ -17294,7 +17640,7 @@
         <v>0</v>
       </c>
       <c r="E361" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F361" s="4">
         <v>5</v>
@@ -17329,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="E362" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F362" s="4">
         <v>5</v>
@@ -17364,7 +17710,7 @@
         <v>0</v>
       </c>
       <c r="E363" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F363" s="4">
         <v>5</v>
@@ -17399,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="E364" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F364" s="4">
         <v>5</v>
@@ -17469,7 +17815,7 @@
         <v>0</v>
       </c>
       <c r="E366" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F366" s="4">
         <v>4</v>
@@ -17504,7 +17850,7 @@
         <v>0</v>
       </c>
       <c r="E367" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F367" s="4">
         <v>4</v>
@@ -17539,7 +17885,7 @@
         <v>0</v>
       </c>
       <c r="E368" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F368" s="4">
         <v>4</v>
@@ -17609,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="E370" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F370" s="4">
         <v>4</v>
@@ -17644,7 +17990,7 @@
         <v>0</v>
       </c>
       <c r="E371" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F371" s="4">
         <v>4</v>
@@ -17679,7 +18025,7 @@
         <v>0</v>
       </c>
       <c r="E372" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F372" s="4">
         <v>4</v>
@@ -17749,7 +18095,7 @@
         <v>0</v>
       </c>
       <c r="E374" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F374" s="4">
         <v>10</v>
@@ -17784,7 +18130,7 @@
         <v>0</v>
       </c>
       <c r="E375" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F375" s="4">
         <v>10</v>
@@ -17819,7 +18165,7 @@
         <v>0</v>
       </c>
       <c r="E376" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F376" s="4">
         <v>10</v>
@@ -17854,7 +18200,7 @@
         <v>1</v>
       </c>
       <c r="E377" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F377" s="4">
         <v>10</v>
@@ -17889,7 +18235,7 @@
         <v>0</v>
       </c>
       <c r="E378" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F378" s="4">
         <v>10</v>
@@ -17924,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="E379" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F379" s="4">
         <v>10</v>
@@ -17959,7 +18305,7 @@
         <v>0</v>
       </c>
       <c r="E380" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F380" s="4">
         <v>10</v>
@@ -17994,7 +18340,7 @@
         <v>0</v>
       </c>
       <c r="E381" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F381" s="4">
         <v>10</v>
@@ -18029,7 +18375,7 @@
         <v>0</v>
       </c>
       <c r="E382" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F382" s="4">
         <v>10</v>
@@ -18099,7 +18445,7 @@
         <v>1</v>
       </c>
       <c r="E384" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F384" s="4">
         <v>11</v>
@@ -18134,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="E385" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F385" s="4">
         <v>11</v>
@@ -18169,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="E386" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F386" s="4">
         <v>11</v>
@@ -18204,7 +18550,7 @@
         <v>0</v>
       </c>
       <c r="E387" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F387" s="4">
         <v>11</v>
@@ -18239,7 +18585,7 @@
         <v>1</v>
       </c>
       <c r="E388" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F388" s="4">
         <v>11</v>
@@ -18274,7 +18620,7 @@
         <v>1</v>
       </c>
       <c r="E389" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F389" s="4">
         <v>11</v>
@@ -18309,7 +18655,7 @@
         <v>0</v>
       </c>
       <c r="E390" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F390" s="4">
         <v>11</v>
@@ -18344,7 +18690,7 @@
         <v>1</v>
       </c>
       <c r="E391" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F391" s="4">
         <v>11</v>
@@ -18379,7 +18725,7 @@
         <v>1</v>
       </c>
       <c r="E392" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F392" s="4">
         <v>11</v>
@@ -18414,7 +18760,7 @@
         <v>1</v>
       </c>
       <c r="E393" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F393" s="4">
         <v>11</v>
@@ -18484,7 +18830,7 @@
         <v>1</v>
       </c>
       <c r="E395" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F395" s="4">
         <v>9</v>
@@ -18519,7 +18865,7 @@
         <v>0</v>
       </c>
       <c r="E396" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F396" s="4">
         <v>9</v>
@@ -18554,7 +18900,7 @@
         <v>1</v>
       </c>
       <c r="E397" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F397" s="4">
         <v>9</v>
@@ -18589,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="E398" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F398" s="4">
         <v>9</v>
@@ -18624,7 +18970,7 @@
         <v>1</v>
       </c>
       <c r="E399" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F399" s="4">
         <v>9</v>
@@ -18659,7 +19005,7 @@
         <v>0</v>
       </c>
       <c r="E400" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F400" s="4">
         <v>9</v>
@@ -18694,7 +19040,7 @@
         <v>0</v>
       </c>
       <c r="E401" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F401" s="4">
         <v>9</v>
@@ -18729,7 +19075,7 @@
         <v>1</v>
       </c>
       <c r="E402" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F402" s="4">
         <v>9</v>
@@ -18747,6 +19093,1238 @@
         <v>1</v>
       </c>
       <c r="K402" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11">
+      <c r="A403" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C403" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="D403" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11">
+      <c r="A404" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C404" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="D404" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11">
+      <c r="A405" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C405" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="D405" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11">
+      <c r="A406" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="C406" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="D406" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11">
+      <c r="A407" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C407" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D407" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11">
+      <c r="A408" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C408" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="D408" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11">
+      <c r="A409" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C409" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="D409" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11">
+      <c r="A410" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C410" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="D410" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11">
+      <c r="A411" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C411" s="9" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11">
+      <c r="A412" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11">
+      <c r="A413" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11">
+      <c r="A414" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11">
+      <c r="A415" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11">
+      <c r="A416" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11">
+      <c r="A417" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11">
+      <c r="A418" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11">
+      <c r="A419" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11">
+      <c r="A420" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B420" t="s">
+        <v>860</v>
+      </c>
+      <c r="C420" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="D420" s="13">
+        <v>1</v>
+      </c>
+      <c r="E420">
+        <v>1</v>
+      </c>
+      <c r="F420">
+        <v>12</v>
+      </c>
+      <c r="G420" t="s">
+        <v>884</v>
+      </c>
+      <c r="H420" t="s">
+        <v>14</v>
+      </c>
+      <c r="I420">
+        <v>2025</v>
+      </c>
+      <c r="J420">
+        <v>1</v>
+      </c>
+      <c r="K420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11">
+      <c r="A421" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B421" t="s">
+        <v>862</v>
+      </c>
+      <c r="C421" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="D421" s="13">
+        <v>0</v>
+      </c>
+      <c r="E421">
+        <v>2</v>
+      </c>
+      <c r="F421">
+        <v>12</v>
+      </c>
+      <c r="G421" t="s">
+        <v>884</v>
+      </c>
+      <c r="H421" t="s">
+        <v>14</v>
+      </c>
+      <c r="I421">
+        <v>2025</v>
+      </c>
+      <c r="J421">
+        <v>1</v>
+      </c>
+      <c r="K421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11">
+      <c r="A422" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B422" t="s">
+        <v>864</v>
+      </c>
+      <c r="C422" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="D422" s="13">
+        <v>0</v>
+      </c>
+      <c r="E422">
+        <v>3</v>
+      </c>
+      <c r="F422">
+        <v>12</v>
+      </c>
+      <c r="G422" t="s">
+        <v>884</v>
+      </c>
+      <c r="H422" t="s">
+        <v>14</v>
+      </c>
+      <c r="I422">
+        <v>2025</v>
+      </c>
+      <c r="J422">
+        <v>1</v>
+      </c>
+      <c r="K422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11">
+      <c r="A423" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B423" t="s">
+        <v>867</v>
+      </c>
+      <c r="C423" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="D423" s="13">
+        <v>1</v>
+      </c>
+      <c r="E423">
+        <v>4</v>
+      </c>
+      <c r="F423">
+        <v>12</v>
+      </c>
+      <c r="G423" t="s">
+        <v>884</v>
+      </c>
+      <c r="H423" t="s">
+        <v>14</v>
+      </c>
+      <c r="I423">
+        <v>2025</v>
+      </c>
+      <c r="J423">
+        <v>1</v>
+      </c>
+      <c r="K423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11">
+      <c r="A424" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B424" t="s">
+        <v>868</v>
+      </c>
+      <c r="C424" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D424" s="13">
+        <v>1</v>
+      </c>
+      <c r="E424">
+        <v>5</v>
+      </c>
+      <c r="F424">
+        <v>12</v>
+      </c>
+      <c r="G424" t="s">
+        <v>884</v>
+      </c>
+      <c r="H424" t="s">
+        <v>14</v>
+      </c>
+      <c r="I424">
+        <v>2025</v>
+      </c>
+      <c r="J424">
+        <v>1</v>
+      </c>
+      <c r="K424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11">
+      <c r="A425" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B425" t="s">
+        <v>870</v>
+      </c>
+      <c r="C425" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="D425" s="13">
+        <v>0</v>
+      </c>
+      <c r="E425">
+        <v>6</v>
+      </c>
+      <c r="F425">
+        <v>12</v>
+      </c>
+      <c r="G425" t="s">
+        <v>884</v>
+      </c>
+      <c r="H425" t="s">
+        <v>14</v>
+      </c>
+      <c r="I425">
+        <v>2025</v>
+      </c>
+      <c r="J425">
+        <v>1</v>
+      </c>
+      <c r="K425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11">
+      <c r="A426" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B426" t="s">
+        <v>872</v>
+      </c>
+      <c r="C426" s="19" t="s">
+        <v>873</v>
+      </c>
+      <c r="D426" s="13">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>7</v>
+      </c>
+      <c r="F426">
+        <v>12</v>
+      </c>
+      <c r="G426" t="s">
+        <v>884</v>
+      </c>
+      <c r="H426" t="s">
+        <v>14</v>
+      </c>
+      <c r="I426">
+        <v>2025</v>
+      </c>
+      <c r="J426">
+        <v>1</v>
+      </c>
+      <c r="K426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11">
+      <c r="A427" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B427" t="s">
+        <v>874</v>
+      </c>
+      <c r="C427" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="D427" s="13">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>8</v>
+      </c>
+      <c r="F427">
+        <v>12</v>
+      </c>
+      <c r="G427" t="s">
+        <v>884</v>
+      </c>
+      <c r="H427" t="s">
+        <v>14</v>
+      </c>
+      <c r="I427">
+        <v>2025</v>
+      </c>
+      <c r="J427">
+        <v>1</v>
+      </c>
+      <c r="K427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11">
+      <c r="A428" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B428" t="s">
+        <v>876</v>
+      </c>
+      <c r="C428" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="D428" s="13">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>9</v>
+      </c>
+      <c r="F428">
+        <v>12</v>
+      </c>
+      <c r="G428" t="s">
+        <v>884</v>
+      </c>
+      <c r="H428" t="s">
+        <v>14</v>
+      </c>
+      <c r="I428">
+        <v>2025</v>
+      </c>
+      <c r="J428">
+        <v>1</v>
+      </c>
+      <c r="K428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11">
+      <c r="A429" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B429" t="s">
+        <v>878</v>
+      </c>
+      <c r="C429" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="D429" s="13">
+        <v>1</v>
+      </c>
+      <c r="E429">
+        <v>10</v>
+      </c>
+      <c r="F429">
+        <v>12</v>
+      </c>
+      <c r="G429" t="s">
+        <v>884</v>
+      </c>
+      <c r="H429" t="s">
+        <v>14</v>
+      </c>
+      <c r="I429">
+        <v>2025</v>
+      </c>
+      <c r="J429">
+        <v>1</v>
+      </c>
+      <c r="K429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11">
+      <c r="A430" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B430" t="s">
+        <v>880</v>
+      </c>
+      <c r="C430" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D430" s="13">
+        <v>0</v>
+      </c>
+      <c r="E430">
+        <v>11</v>
+      </c>
+      <c r="F430">
+        <v>12</v>
+      </c>
+      <c r="G430" t="s">
+        <v>884</v>
+      </c>
+      <c r="H430" t="s">
+        <v>14</v>
+      </c>
+      <c r="I430">
+        <v>2025</v>
+      </c>
+      <c r="J430">
+        <v>1</v>
+      </c>
+      <c r="K430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11">
+      <c r="A431" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B431" t="s">
+        <v>882</v>
+      </c>
+      <c r="C431" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="D431" s="13">
+        <v>0</v>
+      </c>
+      <c r="E431">
+        <v>12</v>
+      </c>
+      <c r="F431">
+        <v>12</v>
+      </c>
+      <c r="G431" t="s">
+        <v>884</v>
+      </c>
+      <c r="H431" t="s">
+        <v>14</v>
+      </c>
+      <c r="I431">
+        <v>2025</v>
+      </c>
+      <c r="J431">
+        <v>1</v>
+      </c>
+      <c r="K431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11">
+      <c r="A432" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="B432" t="s">
+        <v>886</v>
+      </c>
+      <c r="C432" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="D432" s="13">
+        <v>1</v>
+      </c>
+      <c r="E432">
+        <v>1</v>
+      </c>
+      <c r="F432">
+        <v>10</v>
+      </c>
+      <c r="G432" t="s">
+        <v>884</v>
+      </c>
+      <c r="H432" t="s">
+        <v>14</v>
+      </c>
+      <c r="I432">
+        <v>2024</v>
+      </c>
+      <c r="J432">
+        <v>1</v>
+      </c>
+      <c r="K432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14">
+      <c r="B433" t="s">
+        <v>888</v>
+      </c>
+      <c r="C433" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="D433" s="13">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>2</v>
+      </c>
+      <c r="F433">
+        <v>10</v>
+      </c>
+      <c r="G433" t="s">
+        <v>884</v>
+      </c>
+      <c r="H433" t="s">
+        <v>14</v>
+      </c>
+      <c r="I433">
+        <v>2024</v>
+      </c>
+      <c r="J433">
+        <v>1</v>
+      </c>
+      <c r="K433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:14">
+      <c r="B434" t="s">
+        <v>890</v>
+      </c>
+      <c r="C434" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="D434" s="13">
+        <v>1</v>
+      </c>
+      <c r="E434">
+        <v>3</v>
+      </c>
+      <c r="F434">
+        <v>10</v>
+      </c>
+      <c r="G434" t="s">
+        <v>884</v>
+      </c>
+      <c r="H434" t="s">
+        <v>14</v>
+      </c>
+      <c r="I434">
+        <v>2024</v>
+      </c>
+      <c r="J434">
+        <v>1</v>
+      </c>
+      <c r="K434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:14">
+      <c r="B435" t="s">
+        <v>893</v>
+      </c>
+      <c r="C435" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="D435" s="13">
+        <v>1</v>
+      </c>
+      <c r="E435">
+        <v>4</v>
+      </c>
+      <c r="F435">
+        <v>10</v>
+      </c>
+      <c r="G435" t="s">
+        <v>884</v>
+      </c>
+      <c r="H435" t="s">
+        <v>14</v>
+      </c>
+      <c r="I435">
+        <v>2024</v>
+      </c>
+      <c r="J435">
+        <v>1</v>
+      </c>
+      <c r="K435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:14">
+      <c r="B436" t="s">
+        <v>894</v>
+      </c>
+      <c r="C436" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="D436" s="13">
+        <v>1</v>
+      </c>
+      <c r="E436">
+        <v>5</v>
+      </c>
+      <c r="F436">
+        <v>10</v>
+      </c>
+      <c r="G436" t="s">
+        <v>884</v>
+      </c>
+      <c r="H436" t="s">
+        <v>14</v>
+      </c>
+      <c r="I436">
+        <v>2024</v>
+      </c>
+      <c r="J436">
+        <v>1</v>
+      </c>
+      <c r="K436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:14">
+      <c r="B437" t="s">
+        <v>896</v>
+      </c>
+      <c r="C437" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="D437" s="13">
+        <v>0</v>
+      </c>
+      <c r="E437">
+        <v>6</v>
+      </c>
+      <c r="F437">
+        <v>10</v>
+      </c>
+      <c r="G437" t="s">
+        <v>884</v>
+      </c>
+      <c r="H437" t="s">
+        <v>14</v>
+      </c>
+      <c r="I437">
+        <v>2024</v>
+      </c>
+      <c r="J437">
+        <v>1</v>
+      </c>
+      <c r="K437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:14">
+      <c r="B438" t="s">
+        <v>898</v>
+      </c>
+      <c r="C438" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="D438" s="13">
+        <v>0</v>
+      </c>
+      <c r="E438">
+        <v>7</v>
+      </c>
+      <c r="F438">
+        <v>10</v>
+      </c>
+      <c r="G438" t="s">
+        <v>884</v>
+      </c>
+      <c r="H438" t="s">
+        <v>14</v>
+      </c>
+      <c r="I438">
+        <v>2024</v>
+      </c>
+      <c r="J438">
+        <v>1</v>
+      </c>
+      <c r="K438">
+        <v>1</v>
+      </c>
+      <c r="L438" s="20"/>
+      <c r="M438" s="20"/>
+      <c r="N438" s="20"/>
+    </row>
+    <row r="439" spans="1:14">
+      <c r="B439" t="s">
+        <v>900</v>
+      </c>
+      <c r="C439" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="D439" s="13">
+        <v>1</v>
+      </c>
+      <c r="E439">
+        <v>8</v>
+      </c>
+      <c r="F439">
+        <v>10</v>
+      </c>
+      <c r="G439" t="s">
+        <v>884</v>
+      </c>
+      <c r="H439" t="s">
+        <v>14</v>
+      </c>
+      <c r="I439">
+        <v>2024</v>
+      </c>
+      <c r="J439">
+        <v>1</v>
+      </c>
+      <c r="K439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:14">
+      <c r="B440" t="s">
+        <v>902</v>
+      </c>
+      <c r="C440" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="D440" s="13">
+        <v>0</v>
+      </c>
+      <c r="E440">
+        <v>9</v>
+      </c>
+      <c r="F440">
+        <v>10</v>
+      </c>
+      <c r="G440" t="s">
+        <v>884</v>
+      </c>
+      <c r="H440" t="s">
+        <v>14</v>
+      </c>
+      <c r="I440">
+        <v>2024</v>
+      </c>
+      <c r="J440">
+        <v>1</v>
+      </c>
+      <c r="K440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14">
+      <c r="B441" t="s">
+        <v>904</v>
+      </c>
+      <c r="C441" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="D441" s="13">
+        <v>1</v>
+      </c>
+      <c r="E441">
+        <v>10</v>
+      </c>
+      <c r="F441">
+        <v>10</v>
+      </c>
+      <c r="G441" t="s">
+        <v>884</v>
+      </c>
+      <c r="H441" t="s">
+        <v>14</v>
+      </c>
+      <c r="I441">
+        <v>2024</v>
+      </c>
+      <c r="J441">
+        <v>1</v>
+      </c>
+      <c r="K441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:14">
+      <c r="A442" t="s">
+        <v>906</v>
+      </c>
+      <c r="B442" t="s">
+        <v>907</v>
+      </c>
+      <c r="C442" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="D442" s="13">
+        <v>1</v>
+      </c>
+      <c r="E442">
+        <v>1</v>
+      </c>
+      <c r="F442">
+        <v>10</v>
+      </c>
+      <c r="G442" t="s">
+        <v>884</v>
+      </c>
+      <c r="H442" t="s">
+        <v>14</v>
+      </c>
+      <c r="I442">
+        <v>2023</v>
+      </c>
+      <c r="J442">
+        <v>1</v>
+      </c>
+      <c r="K442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14">
+      <c r="B443" t="s">
+        <v>909</v>
+      </c>
+      <c r="C443" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="D443" s="13">
+        <v>0</v>
+      </c>
+      <c r="E443">
+        <v>2</v>
+      </c>
+      <c r="F443">
+        <v>10</v>
+      </c>
+      <c r="G443" t="s">
+        <v>884</v>
+      </c>
+      <c r="H443" t="s">
+        <v>14</v>
+      </c>
+      <c r="I443">
+        <v>2023</v>
+      </c>
+      <c r="J443">
+        <v>1</v>
+      </c>
+      <c r="K443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14">
+      <c r="B444" t="s">
+        <v>911</v>
+      </c>
+      <c r="C444" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="D444" s="13">
+        <v>0</v>
+      </c>
+      <c r="E444">
+        <v>3</v>
+      </c>
+      <c r="F444">
+        <v>10</v>
+      </c>
+      <c r="G444" t="s">
+        <v>884</v>
+      </c>
+      <c r="H444" t="s">
+        <v>14</v>
+      </c>
+      <c r="I444">
+        <v>2023</v>
+      </c>
+      <c r="J444">
+        <v>1</v>
+      </c>
+      <c r="K444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14">
+      <c r="B445" t="s">
+        <v>913</v>
+      </c>
+      <c r="C445" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="D445" s="13">
+        <v>0</v>
+      </c>
+      <c r="E445">
+        <v>4</v>
+      </c>
+      <c r="F445">
+        <v>10</v>
+      </c>
+      <c r="G445" t="s">
+        <v>884</v>
+      </c>
+      <c r="H445" t="s">
+        <v>14</v>
+      </c>
+      <c r="I445">
+        <v>2023</v>
+      </c>
+      <c r="J445">
+        <v>1</v>
+      </c>
+      <c r="K445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14">
+      <c r="B446" t="s">
+        <v>915</v>
+      </c>
+      <c r="C446" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="D446" s="13">
+        <v>1</v>
+      </c>
+      <c r="E446">
+        <v>5</v>
+      </c>
+      <c r="F446">
+        <v>10</v>
+      </c>
+      <c r="G446" t="s">
+        <v>884</v>
+      </c>
+      <c r="H446" t="s">
+        <v>14</v>
+      </c>
+      <c r="I446">
+        <v>2023</v>
+      </c>
+      <c r="J446">
+        <v>1</v>
+      </c>
+      <c r="K446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14">
+      <c r="B447" t="s">
+        <v>917</v>
+      </c>
+      <c r="C447" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="D447" s="13">
+        <v>0</v>
+      </c>
+      <c r="E447">
+        <v>6</v>
+      </c>
+      <c r="F447">
+        <v>10</v>
+      </c>
+      <c r="G447" t="s">
+        <v>884</v>
+      </c>
+      <c r="H447" t="s">
+        <v>14</v>
+      </c>
+      <c r="I447">
+        <v>2023</v>
+      </c>
+      <c r="J447">
+        <v>1</v>
+      </c>
+      <c r="K447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14">
+      <c r="B448" t="s">
+        <v>919</v>
+      </c>
+      <c r="C448" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="D448" s="13">
+        <v>0</v>
+      </c>
+      <c r="E448">
+        <v>7</v>
+      </c>
+      <c r="F448">
+        <v>10</v>
+      </c>
+      <c r="G448" t="s">
+        <v>884</v>
+      </c>
+      <c r="H448" t="s">
+        <v>14</v>
+      </c>
+      <c r="I448">
+        <v>2023</v>
+      </c>
+      <c r="J448">
+        <v>1</v>
+      </c>
+      <c r="K448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="2:11">
+      <c r="B449" t="s">
+        <v>921</v>
+      </c>
+      <c r="C449" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="D449" s="13">
+        <v>1</v>
+      </c>
+      <c r="E449">
+        <v>8</v>
+      </c>
+      <c r="F449">
+        <v>10</v>
+      </c>
+      <c r="G449" t="s">
+        <v>884</v>
+      </c>
+      <c r="H449" t="s">
+        <v>14</v>
+      </c>
+      <c r="I449">
+        <v>2023</v>
+      </c>
+      <c r="J449">
+        <v>1</v>
+      </c>
+      <c r="K449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="2:11">
+      <c r="B450" t="s">
+        <v>923</v>
+      </c>
+      <c r="C450" s="9" t="s">
+        <v>924</v>
+      </c>
+      <c r="D450" s="13">
+        <v>0</v>
+      </c>
+      <c r="E450">
+        <v>9</v>
+      </c>
+      <c r="F450">
+        <v>10</v>
+      </c>
+      <c r="G450" t="s">
+        <v>884</v>
+      </c>
+      <c r="H450" t="s">
+        <v>14</v>
+      </c>
+      <c r="I450">
+        <v>2023</v>
+      </c>
+      <c r="J450">
+        <v>1</v>
+      </c>
+      <c r="K450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="2:11">
+      <c r="B451" t="s">
+        <v>925</v>
+      </c>
+      <c r="C451" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="D451" s="13">
+        <v>1</v>
+      </c>
+      <c r="E451">
+        <v>10</v>
+      </c>
+      <c r="F451">
+        <v>10</v>
+      </c>
+      <c r="G451" t="s">
+        <v>884</v>
+      </c>
+      <c r="H451" t="s">
+        <v>14</v>
+      </c>
+      <c r="I451">
+        <v>2023</v>
+      </c>
+      <c r="J451">
+        <v>1</v>
+      </c>
+      <c r="K451">
         <v>1</v>
       </c>
     </row>
@@ -18825,7 +20403,7 @@
     <row r="8" spans="1:4">
       <c r="A8">
         <f>COUNTIF(Sheet1!D:D,"0")</f>
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B8">
         <f>COUNTIF(Sheet1!D:D," ")</f>
@@ -18833,11 +20411,11 @@
       </c>
       <c r="C8">
         <f>COUNTIF(Sheet1!D:D,"1")</f>
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D8">
         <f>SUM(A8:C8)</f>
-        <v>401</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
